--- a/attendance_history/Present_2026-03-28.xlsx
+++ b/attendance_history/Present_2026-03-28.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -475,17 +475,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TUSUBIRA CALEBU</t>
+          <t xml:space="preserve">sky deal </t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2023-08-16868</t>
+          <t>2024-08-16867</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bcs</t>
+          <t>BBA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -495,32 +495,86 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>0:01:24</t>
+          <t>16:58:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Mwesigwa joshua</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2024-08-28531</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>BBA</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>8:00:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TUSUBIRA CALEBU</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2023-08-16868</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Bcs</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0:01:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>Ssebata Enock</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2024-08-28288</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Law</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>0:00:47</t>
         </is>
